--- a/Trainingschema planner v2.xlsx
+++ b/Trainingschema planner v2.xlsx
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="D157" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" s="130" t="inlineStr"/>
     </row>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="D158" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" s="129" t="inlineStr"/>
     </row>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="D159" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" s="130" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="D160" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" s="129" t="inlineStr"/>
     </row>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="D161" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" s="130" t="inlineStr"/>
     </row>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="D162" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="129" t="inlineStr"/>
     </row>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="D163" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" s="130" t="inlineStr"/>
     </row>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="D164" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" s="129" t="inlineStr"/>
     </row>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="D165" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" s="130" t="inlineStr"/>
     </row>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="D166" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" s="129" t="inlineStr"/>
     </row>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="D177" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E177" s="130" t="inlineStr"/>
     </row>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="D178" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" s="129" t="inlineStr"/>
     </row>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="D179" s="130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" s="130" t="inlineStr"/>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="H1" s="107" t="inlineStr">
         <is>
-          <t>Gegenereerd: 26-06-2026 13:54</t>
+          <t>Gegenereerd: 26-06-2026 14:40</t>
         </is>
       </c>
       <c r="J1" s="87" t="n">
@@ -11657,7 +11657,12 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C56" s="131" t="n"/>
+      <c r="C56" s="118" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D56" s="112" t="inlineStr">
         <is>
           <t>JO15-9
@@ -11690,11 +11695,31 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C57" s="131" t="n"/>
+      <c r="C57" s="118" t="inlineStr">
+        <is>
+          <t>JO16-2
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D57" s="131" t="n"/>
-      <c r="E57" s="131" t="n"/>
-      <c r="F57" s="131" t="n"/>
-      <c r="G57" s="133" t="n"/>
+      <c r="E57" s="118" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="F57" s="118" t="inlineStr">
+        <is>
+          <t>JO16-4
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="G57" s="118" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="52">
       <c r="A58" s="110" t="n"/>
@@ -11703,11 +11728,21 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C58" s="131" t="n"/>
+      <c r="C58" s="118" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D58" s="131" t="n"/>
       <c r="E58" s="131" t="n"/>
       <c r="F58" s="131" t="n"/>
-      <c r="G58" s="131" t="n"/>
+      <c r="G58" s="118" t="inlineStr">
+        <is>
+          <t>JO16-5
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="52">
       <c r="A59" s="96" t="inlineStr">
@@ -11834,7 +11869,12 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C62" s="132" t="n"/>
+      <c r="C62" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D62" s="114" t="inlineStr">
         <is>
           <t>JO15-9
@@ -11867,11 +11907,31 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C63" s="132" t="n"/>
+      <c r="C63" s="120" t="inlineStr">
+        <is>
+          <t>JO16-2
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D63" s="132" t="n"/>
-      <c r="E63" s="132" t="n"/>
-      <c r="F63" s="132" t="n"/>
-      <c r="G63" s="131" t="n"/>
+      <c r="E63" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="F63" s="120" t="inlineStr">
+        <is>
+          <t>JO16-4
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="G63" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="52">
       <c r="A64" s="110" t="n"/>
@@ -11880,11 +11940,21 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C64" s="132" t="n"/>
+      <c r="C64" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D64" s="132" t="n"/>
       <c r="E64" s="132" t="n"/>
       <c r="F64" s="132" t="n"/>
-      <c r="G64" s="132" t="n"/>
+      <c r="G64" s="120" t="inlineStr">
+        <is>
+          <t>JO16-5
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="52">
       <c r="A65" s="96" t="inlineStr">
@@ -12011,7 +12081,12 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C68" s="132" t="n"/>
+      <c r="C68" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D68" s="114" t="inlineStr">
         <is>
           <t>JO15-9
@@ -12044,14 +12119,29 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C69" s="132" t="n"/>
+      <c r="C69" s="120" t="inlineStr">
+        <is>
+          <t>JO16-2
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D69" s="132" t="n"/>
-      <c r="E69" s="132" t="n"/>
-      <c r="F69" s="132" t="n"/>
-      <c r="G69" s="116" t="inlineStr">
-        <is>
-          <t>KT-vrijdag
-18:30-19:30</t>
+      <c r="E69" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="F69" s="120" t="inlineStr">
+        <is>
+          <t>JO16-4
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="G69" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
         </is>
       </c>
     </row>
@@ -12062,11 +12152,21 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C70" s="132" t="n"/>
+      <c r="C70" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D70" s="132" t="n"/>
       <c r="E70" s="132" t="n"/>
       <c r="F70" s="132" t="n"/>
-      <c r="G70" s="131" t="n"/>
+      <c r="G70" s="120" t="inlineStr">
+        <is>
+          <t>JO16-5
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="52">
       <c r="A71" s="96" t="inlineStr">
@@ -12193,7 +12293,12 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C74" s="133" t="n"/>
+      <c r="C74" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D74" s="115" t="inlineStr">
         <is>
           <t>JO15-9
@@ -12226,14 +12331,29 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C75" s="133" t="n"/>
+      <c r="C75" s="120" t="inlineStr">
+        <is>
+          <t>JO16-2
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D75" s="132" t="n"/>
-      <c r="E75" s="132" t="n"/>
-      <c r="F75" s="132" t="n"/>
-      <c r="G75" s="117" t="inlineStr">
-        <is>
-          <t>KT-vrijdag
-18:30-19:30</t>
+      <c r="E75" s="120" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="F75" s="120" t="inlineStr">
+        <is>
+          <t>JO16-4
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="G75" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
         </is>
       </c>
     </row>
@@ -12244,11 +12364,21 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C76" s="133" t="n"/>
+      <c r="C76" s="120" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D76" s="132" t="n"/>
       <c r="E76" s="132" t="n"/>
       <c r="F76" s="133" t="n"/>
-      <c r="G76" s="132" t="n"/>
+      <c r="G76" s="120" t="inlineStr">
+        <is>
+          <t>JO16-5
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="52">
       <c r="A77" s="96" t="inlineStr">
@@ -12261,14 +12391,24 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C77" s="131" t="n"/>
+      <c r="C77" s="118" t="inlineStr">
+        <is>
+          <t>JO16-4
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="D77" s="134" t="inlineStr">
         <is>
           <t>Heren-1
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E77" s="131" t="n"/>
+      <c r="E77" s="118" t="inlineStr">
+        <is>
+          <t>JO16-2
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="F77" s="134" t="inlineStr">
         <is>
           <t>Heren-1
@@ -12296,7 +12436,12 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E78" s="131" t="n"/>
+      <c r="E78" s="118" t="inlineStr">
+        <is>
+          <t>JO16-5
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="F78" s="134" t="inlineStr">
         <is>
           <t>Heren-2
@@ -12335,7 +12480,12 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C80" s="131" t="n"/>
+      <c r="C80" s="123" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D80" s="132" t="n"/>
       <c r="E80" s="131" t="n"/>
       <c r="F80" s="131" t="n"/>
@@ -12348,24 +12498,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C81" s="131" t="n"/>
+      <c r="C81" s="123" t="inlineStr">
+        <is>
+          <t>JO16-2
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D81" s="116" t="inlineStr">
         <is>
           <t>KT-avond
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E81" s="116" t="inlineStr">
-        <is>
-          <t>G-1
-19:00-20:00</t>
-        </is>
-      </c>
-      <c r="F81" s="132" t="n"/>
-      <c r="G81" s="117" t="inlineStr">
-        <is>
-          <t>KT-vrijdag
-18:30-19:30</t>
+      <c r="E81" s="123" t="inlineStr">
+        <is>
+          <t>JO16-1
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="F81" s="123" t="inlineStr">
+        <is>
+          <t>JO16-4
+18:00-19:15</t>
+        </is>
+      </c>
+      <c r="G81" s="123" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
         </is>
       </c>
     </row>
@@ -12376,11 +12536,26 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C82" s="131" t="n"/>
+      <c r="C82" s="123" t="inlineStr">
+        <is>
+          <t>JO16-3
+18:00-19:15</t>
+        </is>
+      </c>
       <c r="D82" s="132" t="n"/>
-      <c r="E82" s="132" t="n"/>
+      <c r="E82" s="116" t="inlineStr">
+        <is>
+          <t>G-1
+19:00-20:00</t>
+        </is>
+      </c>
       <c r="F82" s="131" t="n"/>
-      <c r="G82" s="132" t="n"/>
+      <c r="G82" s="123" t="inlineStr">
+        <is>
+          <t>JO16-5
+18:00-19:15</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="52">
       <c r="A83" s="96" t="inlineStr">
@@ -12393,14 +12568,24 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C83" s="132" t="n"/>
+      <c r="C83" s="120" t="inlineStr">
+        <is>
+          <t>JO16-4
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="D83" s="135" t="inlineStr">
         <is>
           <t>Heren-1
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E83" s="132" t="n"/>
+      <c r="E83" s="120" t="inlineStr">
+        <is>
+          <t>JO16-2
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="F83" s="135" t="inlineStr">
         <is>
           <t>Heren-1
@@ -12428,7 +12613,12 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E84" s="132" t="n"/>
+      <c r="E84" s="120" t="inlineStr">
+        <is>
+          <t>JO16-5
+19:00-20:15</t>
+        </is>
+      </c>
       <c r="F84" s="135" t="inlineStr">
         <is>
           <t>Heren-2
@@ -12487,19 +12677,9 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E87" s="117" t="inlineStr">
-        <is>
-          <t>G-1
-19:00-20:00</t>
-        </is>
-      </c>
+      <c r="E87" s="132" t="n"/>
       <c r="F87" s="133" t="n"/>
-      <c r="G87" s="121" t="inlineStr">
-        <is>
-          <t>KT-vrijdag
-18:30-19:30</t>
-        </is>
-      </c>
+      <c r="G87" s="133" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1" s="52">
       <c r="A88" s="110" t="n"/>
@@ -12510,7 +12690,12 @@
       </c>
       <c r="C88" s="132" t="n"/>
       <c r="D88" s="133" t="n"/>
-      <c r="E88" s="133" t="n"/>
+      <c r="E88" s="117" t="inlineStr">
+        <is>
+          <t>G-1
+19:00-20:00</t>
+        </is>
+      </c>
       <c r="F88" s="132" t="n"/>
       <c r="G88" s="133" t="n"/>
     </row>
@@ -12525,22 +12710,22 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C89" s="118" t="inlineStr">
-        <is>
-          <t>JO16-1
+      <c r="C89" s="120" t="inlineStr">
+        <is>
+          <t>JO16-4
+19:00-20:15</t>
+        </is>
+      </c>
+      <c r="D89" s="118" t="inlineStr">
+        <is>
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D89" s="118" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="E89" s="118" t="inlineStr">
-        <is>
-          <t>JO16-1
-19:30-21:00</t>
+      <c r="E89" s="120" t="inlineStr">
+        <is>
+          <t>JO16-2
+19:00-20:15</t>
         </is>
       </c>
       <c r="F89" s="135" t="inlineStr">
@@ -12565,8 +12750,8 @@
       </c>
       <c r="C90" s="118" t="inlineStr">
         <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="D90" s="135" t="inlineStr">
@@ -12575,10 +12760,10 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E90" s="118" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+      <c r="E90" s="120" t="inlineStr">
+        <is>
+          <t>JO16-5
+19:00-20:15</t>
         </is>
       </c>
       <c r="F90" s="135" t="inlineStr">
@@ -12589,8 +12774,8 @@
       </c>
       <c r="G90" s="118" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-3
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -12603,8 +12788,8 @@
       </c>
       <c r="C91" s="118" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="D91" s="135" t="inlineStr">
@@ -12615,14 +12800,14 @@
       </c>
       <c r="E91" s="118" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
       <c r="F91" s="118" t="inlineStr">
         <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="G91" s="117" t="inlineStr">
@@ -12641,32 +12826,32 @@
       </c>
       <c r="C92" s="118" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
       <c r="D92" s="118" t="inlineStr">
         <is>
-          <t>JO16-6
+          <t>JO17-3
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E92" s="118" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E92" s="118" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="F92" s="118" t="inlineStr">
         <is>
-          <t>JO16-6
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="G92" s="118" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12864,7 @@
       </c>
       <c r="C93" s="118" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
@@ -12689,21 +12874,21 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E93" s="117" t="inlineStr">
-        <is>
-          <t>G-1
-19:00-20:00</t>
+      <c r="E93" s="118" t="inlineStr">
+        <is>
+          <t>JO19-3
+19:30-21:00</t>
         </is>
       </c>
       <c r="F93" s="118" t="inlineStr">
         <is>
-          <t>JO16-9
-19:30-21:00</t>
+          <t>JO17-5
+19:30-20:45</t>
         </is>
       </c>
       <c r="G93" s="118" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -12717,31 +12902,31 @@
       </c>
       <c r="C94" s="118" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
       <c r="D94" s="118" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E94" s="117" t="inlineStr">
+        <is>
+          <t>G-1
+19:00-20:00</t>
+        </is>
+      </c>
+      <c r="F94" s="118" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E94" s="118" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F94" s="118" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G94" s="118" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -12759,20 +12944,20 @@
       </c>
       <c r="C95" s="120" t="inlineStr">
         <is>
-          <t>JO16-1
+          <t>JO16-4
+19:00-20:15</t>
+        </is>
+      </c>
+      <c r="D95" s="120" t="inlineStr">
+        <is>
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D95" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="E95" s="120" t="inlineStr">
         <is>
-          <t>JO16-1
-19:30-21:00</t>
+          <t>JO16-2
+19:00-20:15</t>
         </is>
       </c>
       <c r="F95" s="135" t="inlineStr">
@@ -12797,8 +12982,8 @@
       </c>
       <c r="C96" s="120" t="inlineStr">
         <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="D96" s="135" t="inlineStr">
@@ -12809,8 +12994,8 @@
       </c>
       <c r="E96" s="120" t="inlineStr">
         <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO16-5
+19:00-20:15</t>
         </is>
       </c>
       <c r="F96" s="135" t="inlineStr">
@@ -12821,8 +13006,8 @@
       </c>
       <c r="G96" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-3
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -12835,8 +13020,8 @@
       </c>
       <c r="C97" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="D97" s="135" t="inlineStr">
@@ -12847,14 +13032,14 @@
       </c>
       <c r="E97" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
       <c r="F97" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="G97" s="121" t="inlineStr">
@@ -12873,32 +13058,32 @@
       </c>
       <c r="C98" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
       <c r="D98" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
+          <t>JO17-3
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E98" s="120" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E98" s="120" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="F98" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="G98" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -12911,7 +13096,7 @@
       </c>
       <c r="C99" s="120" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
@@ -12921,21 +13106,21 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E99" s="121" t="inlineStr">
-        <is>
-          <t>G-1
-19:00-20:00</t>
+      <c r="E99" s="120" t="inlineStr">
+        <is>
+          <t>JO19-3
+19:30-21:00</t>
         </is>
       </c>
       <c r="F99" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
-19:30-21:00</t>
+          <t>JO17-5
+19:30-20:45</t>
         </is>
       </c>
       <c r="G99" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -12949,31 +13134,31 @@
       </c>
       <c r="C100" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
       <c r="D100" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E100" s="121" t="inlineStr">
+        <is>
+          <t>G-1
+19:00-20:00</t>
+        </is>
+      </c>
+      <c r="F100" s="120" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E100" s="120" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F100" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G100" s="120" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -12989,22 +13174,22 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C101" s="120" t="inlineStr">
-        <is>
-          <t>JO16-1
+      <c r="C101" s="123" t="inlineStr">
+        <is>
+          <t>JO16-4
+19:00-20:15</t>
+        </is>
+      </c>
+      <c r="D101" s="120" t="inlineStr">
+        <is>
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D101" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="E101" s="120" t="inlineStr">
-        <is>
-          <t>JO16-1
-19:30-21:00</t>
+      <c r="E101" s="123" t="inlineStr">
+        <is>
+          <t>JO16-2
+19:00-20:15</t>
         </is>
       </c>
       <c r="F101" s="135" t="inlineStr">
@@ -13029,8 +13214,8 @@
       </c>
       <c r="C102" s="120" t="inlineStr">
         <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="D102" s="135" t="inlineStr">
@@ -13039,10 +13224,10 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E102" s="120" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+      <c r="E102" s="123" t="inlineStr">
+        <is>
+          <t>JO16-5
+19:00-20:15</t>
         </is>
       </c>
       <c r="F102" s="135" t="inlineStr">
@@ -13053,8 +13238,8 @@
       </c>
       <c r="G102" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-3
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13067,8 +13252,8 @@
       </c>
       <c r="C103" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="D103" s="135" t="inlineStr">
@@ -13079,19 +13264,19 @@
       </c>
       <c r="E103" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
       <c r="F103" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="G103" s="118" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -13105,32 +13290,32 @@
       </c>
       <c r="C104" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
       <c r="D104" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
+          <t>JO17-3
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E104" s="120" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E104" s="120" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="F104" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="G104" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13328,7 @@
       </c>
       <c r="C105" s="120" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
@@ -13153,21 +13338,21 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E105" s="118" t="inlineStr">
-        <is>
-          <t>JO16-12
-20:00-21:30</t>
+      <c r="E105" s="120" t="inlineStr">
+        <is>
+          <t>JO19-3
+19:30-21:00</t>
         </is>
       </c>
       <c r="F105" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
-19:30-21:00</t>
+          <t>JO17-5
+19:30-20:45</t>
         </is>
       </c>
       <c r="G105" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -13181,31 +13366,31 @@
       </c>
       <c r="C106" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
       <c r="D106" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E106" s="118" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F106" s="120" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E106" s="120" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F106" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G106" s="120" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -13221,22 +13406,22 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C107" s="120" t="inlineStr">
-        <is>
-          <t>JO16-1
+      <c r="C107" s="118" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
+        </is>
+      </c>
+      <c r="D107" s="120" t="inlineStr">
+        <is>
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D107" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="E107" s="120" t="inlineStr">
-        <is>
-          <t>JO16-1
-19:30-21:00</t>
+      <c r="E107" s="118" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
         </is>
       </c>
       <c r="F107" s="136" t="inlineStr">
@@ -13261,8 +13446,8 @@
       </c>
       <c r="C108" s="120" t="inlineStr">
         <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="D108" s="136" t="inlineStr">
@@ -13271,12 +13456,7 @@
 19:00-20:30</t>
         </is>
       </c>
-      <c r="E108" s="120" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
-        </is>
-      </c>
+      <c r="E108" s="131" t="n"/>
       <c r="F108" s="136" t="inlineStr">
         <is>
           <t>Heren-2
@@ -13285,8 +13465,8 @@
       </c>
       <c r="G108" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-3
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13299,8 +13479,8 @@
       </c>
       <c r="C109" s="120" t="inlineStr">
         <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="D109" s="136" t="inlineStr">
@@ -13311,19 +13491,19 @@
       </c>
       <c r="E109" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
       <c r="F109" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="G109" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -13337,32 +13517,32 @@
       </c>
       <c r="C110" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
       <c r="D110" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
+          <t>JO17-3
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E110" s="120" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E110" s="120" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="F110" s="120" t="inlineStr">
         <is>
-          <t>JO16-6
-19:30-21:00</t>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="G110" s="120" t="inlineStr">
         <is>
-          <t>JO16-5
-19:30-21:00</t>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13555,7 @@
       </c>
       <c r="C111" s="120" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
@@ -13387,19 +13567,19 @@
       </c>
       <c r="E111" s="120" t="inlineStr">
         <is>
-          <t>JO16-12
-20:00-21:30</t>
+          <t>JO19-3
+19:30-21:00</t>
         </is>
       </c>
       <c r="F111" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
-19:30-21:00</t>
+          <t>JO17-5
+19:30-20:45</t>
         </is>
       </c>
       <c r="G111" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -13413,31 +13593,31 @@
       </c>
       <c r="C112" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
       <c r="D112" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E112" s="120" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F112" s="120" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E112" s="120" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F112" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G112" s="120" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -13455,31 +13635,31 @@
       </c>
       <c r="C113" s="120" t="inlineStr">
         <is>
-          <t>JO16-1
-19:30-21:00</t>
+          <t>JO19-7
+20:15-21:45</t>
         </is>
       </c>
       <c r="D113" s="118" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
       <c r="E113" s="120" t="inlineStr">
         <is>
-          <t>JO16-1
-19:30-21:00</t>
+          <t>JO19-7
+20:15-21:45</t>
         </is>
       </c>
       <c r="F113" s="118" t="inlineStr">
         <is>
-          <t>JO16-14
+          <t>JO19-6
 20:30-22:00</t>
         </is>
       </c>
-      <c r="G113" s="118" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="G113" s="119" t="inlineStr">
+        <is>
+          <t>Heren-11
 20:30-22:00</t>
         </is>
       </c>
@@ -13491,34 +13671,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C114" s="120" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+      <c r="C114" s="123" t="inlineStr">
+        <is>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="D114" s="118" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E114" s="120" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E114" s="119" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
         </is>
       </c>
       <c r="F114" s="118" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="G114" s="120" t="inlineStr">
-        <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G114" s="123" t="inlineStr">
+        <is>
+          <t>JO17-3
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13529,33 +13709,33 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C115" s="120" t="inlineStr">
-        <is>
-          <t>JO16-3
-19:30-21:00</t>
+      <c r="C115" s="123" t="inlineStr">
+        <is>
+          <t>JO17-2
+19:30-20:45</t>
         </is>
       </c>
       <c r="D115" s="118" t="inlineStr">
         <is>
-          <t>JO17-2
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E115" s="120" t="inlineStr">
-        <is>
-          <t>JO16-5
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F115" s="120" t="inlineStr">
-        <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E115" s="123" t="inlineStr">
+        <is>
+          <t>JO17-4
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="F115" s="123" t="inlineStr">
+        <is>
+          <t>JO17-1
+19:30-20:45</t>
         </is>
       </c>
       <c r="G115" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -13569,32 +13749,32 @@
       </c>
       <c r="C116" s="120" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D116" s="120" t="inlineStr">
-        <is>
-          <t>JO16-6
+      <c r="D116" s="123" t="inlineStr">
+        <is>
+          <t>JO17-3
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E116" s="120" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E116" s="120" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F116" s="120" t="inlineStr">
-        <is>
-          <t>JO16-6
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="G116" s="120" t="inlineStr">
-        <is>
-          <t>JO16-5
-19:30-21:00</t>
+      <c r="F116" s="123" t="inlineStr">
+        <is>
+          <t>JO17-2
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="G116" s="123" t="inlineStr">
+        <is>
+          <t>JO17-4
+19:30-20:45</t>
         </is>
       </c>
     </row>
@@ -13607,26 +13787,26 @@
       </c>
       <c r="C117" s="120" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
       <c r="D117" s="132" t="n"/>
       <c r="E117" s="120" t="inlineStr">
         <is>
-          <t>JO16-12
-20:00-21:30</t>
-        </is>
-      </c>
-      <c r="F117" s="120" t="inlineStr">
-        <is>
-          <t>JO16-9
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
+      <c r="F117" s="123" t="inlineStr">
+        <is>
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
       <c r="G117" s="120" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -13640,31 +13820,31 @@
       </c>
       <c r="C118" s="120" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D118" s="120" t="inlineStr">
-        <is>
-          <t>JO16-8
+      <c r="D118" s="123" t="inlineStr">
+        <is>
+          <t>JO17-5
+19:30-20:45</t>
+        </is>
+      </c>
+      <c r="E118" s="120" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F118" s="120" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E118" s="120" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F118" s="120" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G118" s="120" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -13680,33 +13860,33 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C119" s="123" t="inlineStr">
-        <is>
-          <t>JO16-1
-19:30-21:00</t>
+      <c r="C119" s="120" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
         </is>
       </c>
       <c r="D119" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
-      <c r="E119" s="123" t="inlineStr">
-        <is>
-          <t>JO16-1
-19:30-21:00</t>
+      <c r="E119" s="120" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
         </is>
       </c>
       <c r="F119" s="120" t="inlineStr">
         <is>
-          <t>JO16-14
+          <t>JO19-6
 20:30-22:00</t>
         </is>
       </c>
-      <c r="G119" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="G119" s="122" t="inlineStr">
+        <is>
+          <t>Heren-11
 20:30-22:00</t>
         </is>
       </c>
@@ -13718,34 +13898,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C120" s="123" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+      <c r="C120" s="119" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
         </is>
       </c>
       <c r="D120" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E120" s="123" t="inlineStr">
-        <is>
-          <t>JO16-2
-19:30-21:00</t>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E120" s="122" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
         </is>
       </c>
       <c r="F120" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="G120" s="123" t="inlineStr">
-        <is>
-          <t>JO16-3
-19:30-21:00</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G120" s="119" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -13756,33 +13936,33 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C121" s="123" t="inlineStr">
-        <is>
-          <t>JO16-3
-19:30-21:00</t>
+      <c r="C121" s="119" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
         </is>
       </c>
       <c r="D121" s="120" t="inlineStr">
         <is>
-          <t>JO17-2
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E121" s="123" t="inlineStr">
-        <is>
-          <t>JO16-5
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F121" s="123" t="inlineStr">
-        <is>
-          <t>JO16-4
-19:30-21:00</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E121" s="119" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F121" s="119" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G121" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -13796,32 +13976,32 @@
       </c>
       <c r="C122" s="123" t="inlineStr">
         <is>
-          <t>JO16-4
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D122" s="123" t="inlineStr">
-        <is>
-          <t>JO16-6
+      <c r="D122" s="119" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E122" s="123" t="inlineStr">
+        <is>
+          <t>MO17-1
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E122" s="123" t="inlineStr">
-        <is>
-          <t>JO16-7
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F122" s="123" t="inlineStr">
-        <is>
-          <t>JO16-6
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="G122" s="123" t="inlineStr">
-        <is>
-          <t>JO16-5
-19:30-21:00</t>
+      <c r="F122" s="119" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G122" s="119" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -13834,26 +14014,31 @@
       </c>
       <c r="C123" s="123" t="inlineStr">
         <is>
-          <t>JO16-7
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D123" s="133" t="n"/>
-      <c r="E123" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
-20:00-21:30</t>
-        </is>
-      </c>
-      <c r="F123" s="123" t="inlineStr">
-        <is>
-          <t>JO16-9
+      <c r="D123" s="119" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E123" s="123" t="inlineStr">
+        <is>
+          <t>JO19-3
 19:30-21:00</t>
         </is>
       </c>
+      <c r="F123" s="119" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
       <c r="G123" s="123" t="inlineStr">
         <is>
-          <t>JO16-8
+          <t>JO19-1
 19:30-21:00</t>
         </is>
       </c>
@@ -13867,31 +14052,26 @@
       </c>
       <c r="C124" s="123" t="inlineStr">
         <is>
-          <t>JO16-9
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="D124" s="123" t="inlineStr">
-        <is>
-          <t>JO16-8
+      <c r="D124" s="131" t="n"/>
+      <c r="E124" s="120" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F124" s="123" t="inlineStr">
+        <is>
+          <t>JO19-4
 19:30-21:00</t>
         </is>
       </c>
-      <c r="E124" s="123" t="inlineStr">
-        <is>
-          <t>JO16-10
-19:30-21:00</t>
-        </is>
-      </c>
-      <c r="F124" s="123" t="inlineStr">
-        <is>
-          <t>JO16-11
-19:30-21:00</t>
-        </is>
-      </c>
       <c r="G124" s="123" t="inlineStr">
         <is>
-          <t>JO16-10
+          <t>JO19-2
 19:30-21:00</t>
         </is>
       </c>
@@ -13907,34 +14087,34 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C125" s="118" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C125" s="119" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D125" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
-      <c r="E125" s="118" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="E125" s="120" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
+        </is>
+      </c>
+      <c r="F125" s="120" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G125" s="119" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
-        </is>
-      </c>
-      <c r="F125" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-20:30-22:00</t>
-        </is>
-      </c>
-      <c r="G125" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
-20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -13945,34 +14125,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C126" s="118" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
+      <c r="C126" s="122" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
         </is>
       </c>
       <c r="D126" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E126" s="118" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E126" s="122" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
         </is>
       </c>
       <c r="F126" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="G126" s="118" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G126" s="122" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -13983,33 +14163,33 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C127" s="118" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
+      <c r="C127" s="122" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
         </is>
       </c>
       <c r="D127" s="120" t="inlineStr">
         <is>
-          <t>JO17-2
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E127" s="118" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F127" s="118" t="inlineStr">
-        <is>
-          <t>JO17-2
-21:00-22:15</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E127" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F127" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G127" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -14021,34 +14201,34 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C128" s="118" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D128" s="118" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E128" s="118" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F128" s="118" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="G128" s="118" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
+      <c r="C128" s="119" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="D128" s="122" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E128" s="119" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F128" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G128" s="122" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14059,34 +14239,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C129" s="118" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D129" s="118" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E129" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
-20:00-21:30</t>
-        </is>
-      </c>
-      <c r="F129" s="118" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C129" s="119" t="inlineStr">
+        <is>
+          <t>Heren-4
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G129" s="118" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
+      <c r="D129" s="122" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E129" s="119" t="inlineStr">
+        <is>
+          <t>Heren-9
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F129" s="122" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G129" s="119" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -14097,33 +14277,33 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C130" s="118" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C130" s="119" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D130" s="118" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D130" s="119" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E130" s="118" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E130" s="120" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F130" s="119" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F130" s="118" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G130" s="118" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G130" s="119" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -14139,34 +14319,34 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C131" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C131" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D131" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
       <c r="E131" s="120" t="inlineStr">
         <is>
-          <t>JO16-15
+          <t>JO19-7
+20:15-21:45</t>
+        </is>
+      </c>
+      <c r="F131" s="120" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G131" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
-        </is>
-      </c>
-      <c r="F131" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-20:30-22:00</t>
-        </is>
-      </c>
-      <c r="G131" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
-20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -14177,34 +14357,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C132" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
+      <c r="C132" s="122" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
         </is>
       </c>
       <c r="D132" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E132" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E132" s="122" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
         </is>
       </c>
       <c r="F132" s="120" t="inlineStr">
         <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="G132" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G132" s="122" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14215,33 +14395,33 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C133" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
+      <c r="C133" s="122" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
         </is>
       </c>
       <c r="D133" s="120" t="inlineStr">
         <is>
-          <t>JO17-2
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E133" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F133" s="120" t="inlineStr">
-        <is>
-          <t>JO17-2
-21:00-22:15</t>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E133" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F133" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G133" s="123" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-5
 20:00-21:30</t>
         </is>
       </c>
@@ -14253,34 +14433,34 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C134" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D134" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E134" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F134" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="G134" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
+      <c r="C134" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="D134" s="122" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E134" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F134" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G134" s="122" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14291,34 +14471,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C135" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D135" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E135" s="123" t="inlineStr">
-        <is>
-          <t>JO16-12
-20:00-21:30</t>
-        </is>
-      </c>
-      <c r="F135" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C135" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G135" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
+      <c r="D135" s="122" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E135" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F135" s="122" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G135" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -14329,33 +14509,33 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C136" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C136" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D136" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D136" s="122" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E136" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E136" s="123" t="inlineStr">
+        <is>
+          <t>JO19-5
+20:00-21:30</t>
+        </is>
+      </c>
+      <c r="F136" s="122" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F136" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G136" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G136" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -14371,34 +14551,34 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C137" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C137" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D137" s="120" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
-      <c r="E137" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="E137" s="123" t="inlineStr">
+        <is>
+          <t>JO19-7
+20:15-21:45</t>
+        </is>
+      </c>
+      <c r="F137" s="120" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G137" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
-        </is>
-      </c>
-      <c r="F137" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-20:30-22:00</t>
-        </is>
-      </c>
-      <c r="G137" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
-20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -14409,34 +14589,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C138" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="D138" s="123" t="inlineStr">
-        <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E138" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F138" s="123" t="inlineStr">
-        <is>
-          <t>JO17-1
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="G138" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
+      <c r="C138" s="122" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="D138" s="120" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E138" s="122" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="F138" s="120" t="inlineStr">
+        <is>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G138" s="122" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14447,28 +14627,28 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C139" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D139" s="123" t="inlineStr">
-        <is>
-          <t>JO17-2
-20:30-21:45</t>
-        </is>
-      </c>
-      <c r="E139" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F139" s="120" t="inlineStr">
-        <is>
-          <t>JO17-2
-21:00-22:15</t>
+      <c r="C139" s="122" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="D139" s="120" t="inlineStr">
+        <is>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E139" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F139" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G139" s="132" t="n"/>
@@ -14480,34 +14660,34 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C140" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D140" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E140" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F140" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="G140" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
+      <c r="C140" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="D140" s="122" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E140" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F140" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G140" s="122" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14518,29 +14698,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C141" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D141" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E141" s="132" t="n"/>
-      <c r="F141" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C141" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G141" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
+      <c r="D141" s="122" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E141" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F141" s="122" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G141" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -14551,33 +14736,28 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C142" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C142" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D142" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D142" s="122" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E142" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E142" s="132" t="n"/>
+      <c r="F142" s="122" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F142" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G142" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G142" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -14593,34 +14773,29 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C143" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C143" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D143" s="123" t="inlineStr">
         <is>
-          <t>JO16-13
+          <t>JO19-2
 20:30-22:00</t>
         </is>
       </c>
-      <c r="E143" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="E143" s="132" t="n"/>
+      <c r="F143" s="123" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G143" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
-        </is>
-      </c>
-      <c r="F143" s="123" t="inlineStr">
-        <is>
-          <t>JO16-14
-20:30-22:00</t>
-        </is>
-      </c>
-      <c r="G143" s="123" t="inlineStr">
-        <is>
-          <t>JO16-15
-20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -14631,24 +14806,34 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C144" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="D144" s="132" t="n"/>
-      <c r="E144" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F144" s="133" t="n"/>
-      <c r="G144" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
+      <c r="C144" s="122" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="D144" s="123" t="inlineStr">
+        <is>
+          <t>JO19-6
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E144" s="124" t="inlineStr">
+        <is>
+          <t>Heren-3
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="F144" s="123" t="inlineStr">
+        <is>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="G144" s="122" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14659,23 +14844,28 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C145" s="120" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D145" s="132" t="n"/>
-      <c r="E145" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F145" s="120" t="inlineStr">
-        <is>
-          <t>JO17-2
-21:00-22:15</t>
+      <c r="C145" s="122" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="D145" s="123" t="inlineStr">
+        <is>
+          <t>JO19-8
+20:30-22:00</t>
+        </is>
+      </c>
+      <c r="E145" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F145" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G145" s="132" t="n"/>
@@ -14687,34 +14877,34 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C146" s="120" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D146" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E146" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F146" s="120" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="G146" s="120" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
+      <c r="C146" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="D146" s="122" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E146" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F146" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G146" s="122" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14725,29 +14915,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C147" s="120" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D147" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E147" s="133" t="n"/>
-      <c r="F147" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C147" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G147" s="120" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
+      <c r="D147" s="122" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E147" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F147" s="122" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G147" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -14758,33 +14953,28 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C148" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C148" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D148" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D148" s="122" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E148" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E148" s="132" t="n"/>
+      <c r="F148" s="122" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F148" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G148" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G148" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -14800,21 +14990,21 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C149" s="120" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C149" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D149" s="132" t="n"/>
-      <c r="E149" s="120" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="E149" s="133" t="n"/>
+      <c r="F149" s="132" t="n"/>
+      <c r="G149" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F149" s="132" t="n"/>
-      <c r="G149" s="132" t="n"/>
     </row>
     <row r="150" ht="16" customHeight="1" s="52">
       <c r="A150" s="109" t="n"/>
@@ -14823,24 +15013,19 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C150" s="120" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
+      <c r="C150" s="124" t="inlineStr">
+        <is>
+          <t>Heren-13
+20:45-22:15</t>
         </is>
       </c>
       <c r="D150" s="132" t="n"/>
-      <c r="E150" s="123" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
-        </is>
-      </c>
+      <c r="E150" s="133" t="n"/>
       <c r="F150" s="132" t="n"/>
-      <c r="G150" s="123" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
+      <c r="G150" s="124" t="inlineStr">
+        <is>
+          <t>Heren-14
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14851,23 +15036,23 @@
           <t>Veld 2A</t>
         </is>
       </c>
-      <c r="C151" s="123" t="inlineStr">
-        <is>
-          <t>JO17-3
-21:00-22:15</t>
+      <c r="C151" s="124" t="inlineStr">
+        <is>
+          <t>Heren-15
+20:45-22:15</t>
         </is>
       </c>
       <c r="D151" s="132" t="n"/>
-      <c r="E151" s="123" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F151" s="123" t="inlineStr">
-        <is>
-          <t>JO17-2
-21:00-22:15</t>
+      <c r="E151" s="124" t="inlineStr">
+        <is>
+          <t>Heren-6
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="F151" s="124" t="inlineStr">
+        <is>
+          <t>Heren-4
+20:45-22:15</t>
         </is>
       </c>
       <c r="G151" s="132" t="n"/>
@@ -14879,34 +15064,34 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C152" s="123" t="inlineStr">
-        <is>
-          <t>JO17-4
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D152" s="123" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E152" s="123" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="F152" s="123" t="inlineStr">
-        <is>
-          <t>JO17-6
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="G152" s="123" t="inlineStr">
-        <is>
-          <t>JO17-5
-21:00-22:15</t>
+      <c r="C152" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="D152" s="124" t="inlineStr">
+        <is>
+          <t>Heren-12
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E152" s="122" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F152" s="124" t="inlineStr">
+        <is>
+          <t>Heren-5
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G152" s="124" t="inlineStr">
+        <is>
+          <t>Heren-19
+20:45-22:15</t>
         </is>
       </c>
     </row>
@@ -14917,29 +15102,34 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C153" s="123" t="inlineStr">
-        <is>
-          <t>JO17-7
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="D153" s="123" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
-        </is>
-      </c>
-      <c r="E153" s="132" t="n"/>
-      <c r="F153" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C153" s="122" t="inlineStr">
+        <is>
+          <t>Heren-4
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G153" s="123" t="inlineStr">
-        <is>
-          <t>JO17-8
-21:00-22:15</t>
+      <c r="D153" s="124" t="inlineStr">
+        <is>
+          <t>Heren-16
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="E153" s="122" t="inlineStr">
+        <is>
+          <t>Heren-9
+21:00-22:30</t>
+        </is>
+      </c>
+      <c r="F153" s="124" t="inlineStr">
+        <is>
+          <t>Heren-8
+20:45-22:15</t>
+        </is>
+      </c>
+      <c r="G153" s="122" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -14950,33 +15140,28 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C154" s="120" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C154" s="122" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D154" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D154" s="122" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E154" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E154" s="133" t="n"/>
+      <c r="F154" s="122" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F154" s="120" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G154" s="120" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G154" s="122" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -14992,21 +15177,21 @@
           <t>Veld 1A</t>
         </is>
       </c>
-      <c r="C155" s="123" t="inlineStr">
-        <is>
-          <t>JO16-12
+      <c r="C155" s="124" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
       <c r="D155" s="133" t="n"/>
-      <c r="E155" s="123" t="inlineStr">
-        <is>
-          <t>JO16-15
+      <c r="E155" s="133" t="n"/>
+      <c r="F155" s="133" t="n"/>
+      <c r="G155" s="124" t="inlineStr">
+        <is>
+          <t>Heren-7
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F155" s="133" t="n"/>
-      <c r="G155" s="133" t="n"/>
     </row>
     <row r="156" ht="16" customHeight="1" s="52">
       <c r="A156" s="109" t="n"/>
@@ -15015,12 +15200,7 @@
           <t>Veld 1B</t>
         </is>
       </c>
-      <c r="C156" s="123" t="inlineStr">
-        <is>
-          <t>JO16-14
-21:00-22:30</t>
-        </is>
-      </c>
+      <c r="C156" s="133" t="n"/>
       <c r="D156" s="133" t="n"/>
       <c r="E156" s="133" t="n"/>
       <c r="F156" s="133" t="n"/>
@@ -15046,9 +15226,19 @@
           <t>Veld 2B</t>
         </is>
       </c>
-      <c r="C158" s="133" t="n"/>
+      <c r="C158" s="124" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
       <c r="D158" s="133" t="n"/>
-      <c r="E158" s="133" t="n"/>
+      <c r="E158" s="124" t="inlineStr">
+        <is>
+          <t>Heren-7
+21:00-22:30</t>
+        </is>
+      </c>
       <c r="F158" s="133" t="n"/>
       <c r="G158" s="133" t="n"/>
     </row>
@@ -15059,16 +15249,26 @@
           <t>Veld 3A</t>
         </is>
       </c>
-      <c r="C159" s="133" t="n"/>
+      <c r="C159" s="124" t="inlineStr">
+        <is>
+          <t>Heren-4
+21:00-22:30</t>
+        </is>
+      </c>
       <c r="D159" s="133" t="n"/>
-      <c r="E159" s="133" t="n"/>
-      <c r="F159" s="123" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="E159" s="124" t="inlineStr">
+        <is>
+          <t>Heren-9
 21:00-22:30</t>
         </is>
       </c>
-      <c r="G159" s="133" t="n"/>
+      <c r="F159" s="133" t="n"/>
+      <c r="G159" s="124" t="inlineStr">
+        <is>
+          <t>Dames-2
+21:00-22:30</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="52">
       <c r="A160" s="110" t="n"/>
@@ -15077,33 +15277,28 @@
           <t>Veld 3B</t>
         </is>
       </c>
-      <c r="C160" s="123" t="inlineStr">
-        <is>
-          <t>MO17-1
+      <c r="C160" s="124" t="inlineStr">
+        <is>
+          <t>Heren-5
 21:00-22:30</t>
         </is>
       </c>
-      <c r="D160" s="123" t="inlineStr">
-        <is>
-          <t>JO19-2
+      <c r="D160" s="124" t="inlineStr">
+        <is>
+          <t>Heren-18
 21:00-22:30</t>
         </is>
       </c>
-      <c r="E160" s="123" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="E160" s="133" t="n"/>
+      <c r="F160" s="124" t="inlineStr">
+        <is>
+          <t>Heren-10
 21:00-22:30</t>
         </is>
       </c>
-      <c r="F160" s="123" t="inlineStr">
-        <is>
-          <t>JO19-2
-21:00-22:30</t>
-        </is>
-      </c>
-      <c r="G160" s="123" t="inlineStr">
-        <is>
-          <t>JO19-1
+      <c r="G160" s="124" t="inlineStr">
+        <is>
+          <t>Heren-6
 21:00-22:30</t>
         </is>
       </c>
@@ -15299,7 +15494,7 @@
       </c>
       <c r="F172" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G172" s="126" t="inlineStr">
@@ -15447,7 +15642,7 @@
       </c>
       <c r="F176" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 1C</t>
         </is>
       </c>
       <c r="G176" s="126" t="inlineStr">
@@ -19243,22 +19438,22 @@
       </c>
       <c r="C279" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D279" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E279" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F279" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G279" s="126" t="inlineStr">
@@ -19280,22 +19475,22 @@
       </c>
       <c r="C280" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D280" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E280" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F280" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G280" s="126" t="inlineStr">
@@ -19317,22 +19512,22 @@
       </c>
       <c r="C281" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D281" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E281" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F281" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G281" s="126" t="inlineStr">
@@ -19354,12 +19549,12 @@
       </c>
       <c r="C282" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D282" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E282" s="125" t="inlineStr">
@@ -19369,7 +19564,7 @@
       </c>
       <c r="F282" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G282" s="126" t="inlineStr">
@@ -19391,22 +19586,22 @@
       </c>
       <c r="C283" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D283" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E283" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F283" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G283" s="126" t="inlineStr">
@@ -19428,22 +19623,22 @@
       </c>
       <c r="C284" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D284" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E284" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F284" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G284" s="126" t="inlineStr">
@@ -19465,22 +19660,22 @@
       </c>
       <c r="C285" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D285" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E285" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F285" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G285" s="126" t="inlineStr">
@@ -19502,22 +19697,22 @@
       </c>
       <c r="C286" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D286" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E286" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F286" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G286" s="126" t="inlineStr">
@@ -19539,22 +19734,22 @@
       </c>
       <c r="C287" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D287" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E287" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F287" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G287" s="126" t="inlineStr">
@@ -19576,22 +19771,22 @@
       </c>
       <c r="C288" s="125" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D288" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E288" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F288" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G288" s="126" t="inlineStr">
@@ -19603,12 +19798,12 @@
     <row r="289">
       <c r="A289" s="125" t="inlineStr">
         <is>
-          <t>JO16-6</t>
+          <t>JO17-1</t>
         </is>
       </c>
       <c r="B289" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C289" s="125" t="inlineStr">
@@ -19618,7 +19813,7 @@
       </c>
       <c r="D289" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E289" s="125" t="inlineStr">
@@ -19628,7 +19823,7 @@
       </c>
       <c r="F289" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G289" s="126" t="inlineStr">
@@ -19640,12 +19835,12 @@
     <row r="290">
       <c r="A290" s="125" t="inlineStr">
         <is>
-          <t>JO16-6</t>
+          <t>JO17-1</t>
         </is>
       </c>
       <c r="B290" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C290" s="125" t="inlineStr">
@@ -19655,17 +19850,17 @@
       </c>
       <c r="D290" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E290" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F290" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G290" s="126" t="inlineStr">
@@ -19677,12 +19872,12 @@
     <row r="291">
       <c r="A291" s="125" t="inlineStr">
         <is>
-          <t>JO16-7</t>
+          <t>JO17-2</t>
         </is>
       </c>
       <c r="B291" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C291" s="125" t="inlineStr">
@@ -19692,17 +19887,17 @@
       </c>
       <c r="D291" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E291" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F291" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G291" s="126" t="inlineStr">
@@ -19714,12 +19909,12 @@
     <row r="292">
       <c r="A292" s="125" t="inlineStr">
         <is>
-          <t>JO16-7</t>
+          <t>JO17-2</t>
         </is>
       </c>
       <c r="B292" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C292" s="125" t="inlineStr">
@@ -19729,7 +19924,7 @@
       </c>
       <c r="D292" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E292" s="125" t="inlineStr">
@@ -19739,7 +19934,7 @@
       </c>
       <c r="F292" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G292" s="126" t="inlineStr">
@@ -19751,12 +19946,12 @@
     <row r="293">
       <c r="A293" s="125" t="inlineStr">
         <is>
-          <t>JO16-8</t>
+          <t>JO17-3</t>
         </is>
       </c>
       <c r="B293" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C293" s="125" t="inlineStr">
@@ -19766,17 +19961,17 @@
       </c>
       <c r="D293" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E293" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F293" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G293" s="126" t="inlineStr">
@@ -19788,12 +19983,12 @@
     <row r="294">
       <c r="A294" s="125" t="inlineStr">
         <is>
-          <t>JO16-8</t>
+          <t>JO17-3</t>
         </is>
       </c>
       <c r="B294" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="C294" s="125" t="inlineStr">
@@ -19803,17 +19998,17 @@
       </c>
       <c r="D294" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E294" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F294" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G294" s="126" t="inlineStr">
@@ -19825,12 +20020,12 @@
     <row r="295">
       <c r="A295" s="125" t="inlineStr">
         <is>
-          <t>JO16-9</t>
+          <t>JO17-4</t>
         </is>
       </c>
       <c r="B295" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C295" s="125" t="inlineStr">
@@ -19840,17 +20035,17 @@
       </c>
       <c r="D295" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E295" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F295" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G295" s="126" t="inlineStr">
@@ -19862,12 +20057,12 @@
     <row r="296">
       <c r="A296" s="125" t="inlineStr">
         <is>
-          <t>JO16-9</t>
+          <t>JO17-4</t>
         </is>
       </c>
       <c r="B296" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="C296" s="125" t="inlineStr">
@@ -19877,17 +20072,17 @@
       </c>
       <c r="D296" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E296" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F296" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G296" s="126" t="inlineStr">
@@ -19899,12 +20094,12 @@
     <row r="297">
       <c r="A297" s="125" t="inlineStr">
         <is>
-          <t>JO16-10</t>
+          <t>JO17-5</t>
         </is>
       </c>
       <c r="B297" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C297" s="125" t="inlineStr">
@@ -19914,7 +20109,7 @@
       </c>
       <c r="D297" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E297" s="125" t="inlineStr">
@@ -19936,12 +20131,12 @@
     <row r="298">
       <c r="A298" s="125" t="inlineStr">
         <is>
-          <t>JO16-10</t>
+          <t>JO17-5</t>
         </is>
       </c>
       <c r="B298" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C298" s="125" t="inlineStr">
@@ -19951,7 +20146,7 @@
       </c>
       <c r="D298" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E298" s="125" t="inlineStr">
@@ -19961,7 +20156,7 @@
       </c>
       <c r="F298" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G298" s="126" t="inlineStr">
@@ -19973,12 +20168,12 @@
     <row r="299">
       <c r="A299" s="125" t="inlineStr">
         <is>
-          <t>JO16-11</t>
+          <t>MO17-1</t>
         </is>
       </c>
       <c r="B299" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C299" s="125" t="inlineStr">
@@ -19993,12 +20188,12 @@
       </c>
       <c r="E299" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F299" s="125" t="inlineStr">
         <is>
-          <t>Veld 1C</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G299" s="126" t="inlineStr">
@@ -20010,12 +20205,12 @@
     <row r="300">
       <c r="A300" s="125" t="inlineStr">
         <is>
-          <t>JO16-11</t>
+          <t>MO17-1</t>
         </is>
       </c>
       <c r="B300" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C300" s="125" t="inlineStr">
@@ -20030,12 +20225,12 @@
       </c>
       <c r="E300" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F300" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G300" s="126" t="inlineStr">
@@ -20047,32 +20242,32 @@
     <row r="301">
       <c r="A301" s="125" t="inlineStr">
         <is>
-          <t>JO16-12</t>
+          <t>JO19-1</t>
         </is>
       </c>
       <c r="B301" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C301" s="125" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D301" s="125" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="D301" s="125" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
       <c r="E301" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F301" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 1C</t>
         </is>
       </c>
       <c r="G301" s="126" t="inlineStr">
@@ -20084,22 +20279,22 @@
     <row r="302">
       <c r="A302" s="125" t="inlineStr">
         <is>
-          <t>JO16-12</t>
+          <t>JO19-1</t>
         </is>
       </c>
       <c r="B302" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="C302" s="125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D302" s="125" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E302" s="125" t="inlineStr">
@@ -20121,7 +20316,7 @@
     <row r="303">
       <c r="A303" s="125" t="inlineStr">
         <is>
-          <t>JO16-13</t>
+          <t>JO19-2</t>
         </is>
       </c>
       <c r="B303" s="125" t="inlineStr">
@@ -20131,22 +20326,22 @@
       </c>
       <c r="C303" s="125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D303" s="125" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E303" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F303" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G303" s="126" t="inlineStr">
@@ -20158,7 +20353,7 @@
     <row r="304">
       <c r="A304" s="125" t="inlineStr">
         <is>
-          <t>JO16-13</t>
+          <t>JO19-2</t>
         </is>
       </c>
       <c r="B304" s="125" t="inlineStr">
@@ -20195,32 +20390,32 @@
     <row r="305">
       <c r="A305" s="125" t="inlineStr">
         <is>
-          <t>JO16-14</t>
+          <t>JO19-3</t>
         </is>
       </c>
       <c r="B305" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C305" s="125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D305" s="125" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E305" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F305" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G305" s="126" t="inlineStr">
@@ -20232,7 +20427,7 @@
     <row r="306">
       <c r="A306" s="125" t="inlineStr">
         <is>
-          <t>JO16-14</t>
+          <t>JO19-3</t>
         </is>
       </c>
       <c r="B306" s="125" t="inlineStr">
@@ -20242,22 +20437,22 @@
       </c>
       <c r="C306" s="125" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D306" s="125" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="D306" s="125" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
       <c r="E306" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F306" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G306" s="126" t="inlineStr">
@@ -20269,32 +20464,32 @@
     <row r="307">
       <c r="A307" s="125" t="inlineStr">
         <is>
-          <t>JO16-15</t>
+          <t>JO19-4</t>
         </is>
       </c>
       <c r="B307" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C307" s="125" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D307" s="125" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="D307" s="125" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
       <c r="E307" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F307" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G307" s="126" t="inlineStr">
@@ -20306,32 +20501,32 @@
     <row r="308">
       <c r="A308" s="125" t="inlineStr">
         <is>
-          <t>JO16-15</t>
+          <t>JO19-4</t>
         </is>
       </c>
       <c r="B308" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C308" s="125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D308" s="125" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E308" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F308" s="125" t="inlineStr">
         <is>
-          <t>Veld 6A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G308" s="126" t="inlineStr">
@@ -20343,32 +20538,32 @@
     <row r="309">
       <c r="A309" s="125" t="inlineStr">
         <is>
-          <t>JO17-1</t>
+          <t>JO19-5</t>
         </is>
       </c>
       <c r="B309" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C309" s="125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D309" s="125" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="E309" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F309" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G309" s="126" t="inlineStr">
@@ -20380,32 +20575,32 @@
     <row r="310">
       <c r="A310" s="125" t="inlineStr">
         <is>
-          <t>JO17-1</t>
+          <t>JO19-5</t>
         </is>
       </c>
       <c r="B310" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="C310" s="125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D310" s="125" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="E310" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F310" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G310" s="126" t="inlineStr">
@@ -20417,12 +20612,12 @@
     <row r="311">
       <c r="A311" s="125" t="inlineStr">
         <is>
-          <t>JO17-2</t>
+          <t>JO19-6</t>
         </is>
       </c>
       <c r="B311" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C311" s="125" t="inlineStr">
@@ -20432,17 +20627,17 @@
       </c>
       <c r="D311" s="125" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E311" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F311" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G311" s="126" t="inlineStr">
@@ -20454,32 +20649,32 @@
     <row r="312">
       <c r="A312" s="125" t="inlineStr">
         <is>
-          <t>JO17-2</t>
+          <t>JO19-6</t>
         </is>
       </c>
       <c r="B312" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C312" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D312" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E312" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F312" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G312" s="126" t="inlineStr">
@@ -20491,32 +20686,32 @@
     <row r="313">
       <c r="A313" s="125" t="inlineStr">
         <is>
-          <t>JO17-3</t>
+          <t>JO19-7</t>
         </is>
       </c>
       <c r="B313" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C313" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="D313" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="E313" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F313" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G313" s="126" t="inlineStr">
@@ -20528,22 +20723,22 @@
     <row r="314">
       <c r="A314" s="125" t="inlineStr">
         <is>
-          <t>JO17-3</t>
+          <t>JO19-7</t>
         </is>
       </c>
       <c r="B314" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C314" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="D314" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="E314" s="125" t="inlineStr">
@@ -20553,7 +20748,7 @@
       </c>
       <c r="F314" s="125" t="inlineStr">
         <is>
-          <t>Veld 6B</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G314" s="126" t="inlineStr">
@@ -20565,22 +20760,22 @@
     <row r="315">
       <c r="A315" s="125" t="inlineStr">
         <is>
-          <t>JO17-4</t>
+          <t>JO19-8</t>
         </is>
       </c>
       <c r="B315" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C315" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D315" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E315" s="125" t="inlineStr">
@@ -20602,22 +20797,22 @@
     <row r="316">
       <c r="A316" s="125" t="inlineStr">
         <is>
-          <t>JO17-4</t>
+          <t>JO19-8</t>
         </is>
       </c>
       <c r="B316" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C316" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D316" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E316" s="125" t="inlineStr">
@@ -20627,7 +20822,7 @@
       </c>
       <c r="F316" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G316" s="126" t="inlineStr">
@@ -20639,7 +20834,7 @@
     <row r="317">
       <c r="A317" s="125" t="inlineStr">
         <is>
-          <t>JO17-5</t>
+          <t>Heren-3</t>
         </is>
       </c>
       <c r="B317" s="125" t="inlineStr">
@@ -20649,22 +20844,22 @@
       </c>
       <c r="C317" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D317" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E317" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F317" s="125" t="inlineStr">
         <is>
-          <t>Veld 7A</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G317" s="126" t="inlineStr">
@@ -20676,17 +20871,17 @@
     <row r="318">
       <c r="A318" s="125" t="inlineStr">
         <is>
-          <t>JO17-5</t>
+          <t>Heren-4</t>
         </is>
       </c>
       <c r="B318" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C318" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D318" s="125" t="inlineStr">
@@ -20701,7 +20896,7 @@
       </c>
       <c r="F318" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G318" s="126" t="inlineStr">
@@ -20713,17 +20908,17 @@
     <row r="319">
       <c r="A319" s="125" t="inlineStr">
         <is>
-          <t>JO17-6</t>
+          <t>Heren-5</t>
         </is>
       </c>
       <c r="B319" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C319" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D319" s="125" t="inlineStr">
@@ -20750,17 +20945,17 @@
     <row r="320">
       <c r="A320" s="125" t="inlineStr">
         <is>
-          <t>JO17-6</t>
+          <t>Heren-6</t>
         </is>
       </c>
       <c r="B320" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C320" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D320" s="125" t="inlineStr">
@@ -20775,7 +20970,7 @@
       </c>
       <c r="F320" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G320" s="126" t="inlineStr">
@@ -20787,12 +20982,12 @@
     <row r="321">
       <c r="A321" s="125" t="inlineStr">
         <is>
-          <t>JO17-7</t>
+          <t>Heren-7</t>
         </is>
       </c>
       <c r="B321" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C321" s="125" t="inlineStr">
@@ -20802,17 +20997,17 @@
       </c>
       <c r="D321" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E321" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F321" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G321" s="126" t="inlineStr">
@@ -20824,17 +21019,17 @@
     <row r="322">
       <c r="A322" s="125" t="inlineStr">
         <is>
-          <t>JO17-7</t>
+          <t>Heren-8</t>
         </is>
       </c>
       <c r="B322" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C322" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D322" s="125" t="inlineStr">
@@ -20844,12 +21039,12 @@
       </c>
       <c r="E322" s="125" t="inlineStr">
         <is>
-          <t>Veld 7</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F322" s="125" t="inlineStr">
         <is>
-          <t>Veld 7B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G322" s="126" t="inlineStr">
@@ -20861,12 +21056,12 @@
     <row r="323">
       <c r="A323" s="125" t="inlineStr">
         <is>
-          <t>JO17-8</t>
+          <t>Heren-9</t>
         </is>
       </c>
       <c r="B323" s="125" t="inlineStr">
         <is>
-          <t>Vrijdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="C323" s="125" t="inlineStr">
@@ -20876,7 +21071,7 @@
       </c>
       <c r="D323" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E323" s="125" t="inlineStr">
@@ -20898,12 +21093,12 @@
     <row r="324">
       <c r="A324" s="125" t="inlineStr">
         <is>
-          <t>JO17-8</t>
+          <t>Heren-10</t>
         </is>
       </c>
       <c r="B324" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="C324" s="125" t="inlineStr">
@@ -20913,7 +21108,7 @@
       </c>
       <c r="D324" s="125" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E324" s="125" t="inlineStr">
@@ -20923,7 +21118,7 @@
       </c>
       <c r="F324" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G324" s="126" t="inlineStr">
@@ -20935,32 +21130,32 @@
     <row r="325">
       <c r="A325" s="125" t="inlineStr">
         <is>
-          <t>MO17-1</t>
+          <t>Heren-11</t>
         </is>
       </c>
       <c r="B325" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="C325" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D325" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E325" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F325" s="125" t="inlineStr">
         <is>
-          <t>Veld 1A</t>
+          <t>Veld 6A</t>
         </is>
       </c>
       <c r="G325" s="126" t="inlineStr">
@@ -20972,32 +21167,32 @@
     <row r="326">
       <c r="A326" s="125" t="inlineStr">
         <is>
-          <t>MO17-1</t>
+          <t>Heren-12</t>
         </is>
       </c>
       <c r="B326" s="125" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C326" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D326" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E326" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F326" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 7B</t>
         </is>
       </c>
       <c r="G326" s="126" t="inlineStr">
@@ -21009,32 +21204,32 @@
     <row r="327">
       <c r="A327" s="125" t="inlineStr">
         <is>
-          <t>JO19-1</t>
+          <t>Heren-13</t>
         </is>
       </c>
       <c r="B327" s="125" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C327" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D327" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E327" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F327" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G327" s="126" t="inlineStr">
@@ -21046,7 +21241,7 @@
     <row r="328">
       <c r="A328" s="125" t="inlineStr">
         <is>
-          <t>JO19-1</t>
+          <t>Heren-14</t>
         </is>
       </c>
       <c r="B328" s="125" t="inlineStr">
@@ -21056,22 +21251,22 @@
       </c>
       <c r="C328" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D328" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E328" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 6</t>
         </is>
       </c>
       <c r="F328" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 6B</t>
         </is>
       </c>
       <c r="G328" s="126" t="inlineStr">
@@ -21083,32 +21278,32 @@
     <row r="329">
       <c r="A329" s="125" t="inlineStr">
         <is>
-          <t>JO19-2</t>
+          <t>Heren-15</t>
         </is>
       </c>
       <c r="B329" s="125" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Maandag</t>
         </is>
       </c>
       <c r="C329" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D329" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E329" s="125" t="inlineStr">
         <is>
-          <t>Veld 1</t>
+          <t>Veld 7</t>
         </is>
       </c>
       <c r="F329" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 7A</t>
         </is>
       </c>
       <c r="G329" s="126" t="inlineStr">
@@ -21120,22 +21315,22 @@
     <row r="330">
       <c r="A330" s="125" t="inlineStr">
         <is>
-          <t>JO19-2</t>
+          <t>Heren-16</t>
         </is>
       </c>
       <c r="B330" s="125" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="C330" s="125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D330" s="125" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="E330" s="125" t="inlineStr">
@@ -21145,7 +21340,7 @@
       </c>
       <c r="F330" s="125" t="inlineStr">
         <is>
-          <t>Veld 1B</t>
+          <t>Veld 1A</t>
         </is>
       </c>
       <c r="G330" s="126" t="inlineStr">
@@ -21157,7 +21352,7 @@
     <row r="331">
       <c r="A331" s="125" t="inlineStr">
         <is>
-          <t>JO13-2</t>
+          <t>Heren-18</t>
         </is>
       </c>
       <c r="B331" s="125" t="inlineStr">
@@ -21167,22 +21362,22 @@
       </c>
       <c r="C331" s="125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D331" s="125" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="E331" s="125" t="inlineStr">
         <is>
-          <t>Veld 6</t>
+          <t>Veld 1</t>
         </is>
       </c>
       <c r="F331" s="125" t="inlineStr">
         <is>
-          <t>Veld 6C</t>
+          <t>Veld 1B</t>
         </is>
       </c>
       <c r="G331" s="126" t="inlineStr">
@@ -21194,138 +21389,446 @@
     <row r="332">
       <c r="A332" s="125" t="inlineStr">
         <is>
+          <t>Heren-19</t>
+        </is>
+      </c>
+      <c r="B332" s="125" t="inlineStr">
+        <is>
+          <t>Vrijdag</t>
+        </is>
+      </c>
+      <c r="C332" s="125" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="D332" s="125" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="E332" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7</t>
+        </is>
+      </c>
+      <c r="F332" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7B</t>
+        </is>
+      </c>
+      <c r="G332" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="125" t="inlineStr">
+        <is>
+          <t>Dames-2</t>
+        </is>
+      </c>
+      <c r="B333" s="125" t="inlineStr">
+        <is>
+          <t>Vrijdag</t>
+        </is>
+      </c>
+      <c r="C333" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D333" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E333" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F333" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1A</t>
+        </is>
+      </c>
+      <c r="G333" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="125" t="inlineStr">
+        <is>
+          <t>JO13-2</t>
+        </is>
+      </c>
+      <c r="B334" s="125" t="inlineStr">
+        <is>
+          <t>Dinsdag</t>
+        </is>
+      </c>
+      <c r="C334" s="125" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D334" s="125" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E334" s="125" t="inlineStr">
+        <is>
+          <t>Veld 6</t>
+        </is>
+      </c>
+      <c r="F334" s="125" t="inlineStr">
+        <is>
+          <t>Veld 6C</t>
+        </is>
+      </c>
+      <c r="G334" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="125" t="inlineStr">
+        <is>
           <t>JO13-3</t>
         </is>
       </c>
-      <c r="B332" s="125" t="inlineStr">
+      <c r="B335" s="125" t="inlineStr">
         <is>
           <t>Dinsdag</t>
         </is>
       </c>
-      <c r="C332" s="125" t="inlineStr">
+      <c r="C335" s="125" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D332" s="125" t="inlineStr">
+      <c r="D335" s="125" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="E332" s="125" t="inlineStr">
+      <c r="E335" s="125" t="inlineStr">
         <is>
           <t>Veld 6</t>
         </is>
       </c>
-      <c r="F332" s="125" t="inlineStr">
+      <c r="F335" s="125" t="inlineStr">
         <is>
           <t>Veld 6D</t>
         </is>
       </c>
-      <c r="G332" s="126" t="inlineStr">
+      <c r="G335" s="126" t="inlineStr">
         <is>
           <t>Ingepland</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" s="125" t="n"/>
-      <c r="B333" s="125" t="n"/>
-      <c r="C333" s="125" t="n"/>
-      <c r="D333" s="125" t="n"/>
-      <c r="E333" s="125" t="n"/>
-      <c r="F333" s="125" t="n"/>
-      <c r="G333" s="126" t="n"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="125" t="n"/>
-      <c r="B334" s="125" t="n"/>
-      <c r="C334" s="125" t="n"/>
-      <c r="D334" s="125" t="n"/>
-      <c r="E334" s="125" t="n"/>
-      <c r="F334" s="125" t="n"/>
-      <c r="G334" s="126" t="n"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="125" t="n"/>
-      <c r="B335" s="125" t="n"/>
-      <c r="C335" s="125" t="n"/>
-      <c r="D335" s="125" t="n"/>
-      <c r="E335" s="125" t="n"/>
-      <c r="F335" s="125" t="n"/>
-      <c r="G335" s="126" t="n"/>
-    </row>
     <row r="336">
-      <c r="A336" s="125" t="n"/>
-      <c r="B336" s="125" t="n"/>
-      <c r="C336" s="125" t="n"/>
-      <c r="D336" s="125" t="n"/>
-      <c r="E336" s="125" t="n"/>
-      <c r="F336" s="125" t="n"/>
-      <c r="G336" s="126" t="n"/>
+      <c r="A336" s="125" t="inlineStr">
+        <is>
+          <t>Dames-2</t>
+        </is>
+      </c>
+      <c r="B336" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C336" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D336" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E336" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7</t>
+        </is>
+      </c>
+      <c r="F336" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7B</t>
+        </is>
+      </c>
+      <c r="G336" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="125" t="n"/>
-      <c r="B337" s="125" t="n"/>
-      <c r="C337" s="125" t="n"/>
-      <c r="D337" s="125" t="n"/>
-      <c r="E337" s="125" t="n"/>
-      <c r="F337" s="125" t="n"/>
-      <c r="G337" s="126" t="n"/>
+      <c r="A337" s="125" t="inlineStr">
+        <is>
+          <t>Heren-3</t>
+        </is>
+      </c>
+      <c r="B337" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C337" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D337" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E337" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7</t>
+        </is>
+      </c>
+      <c r="F337" s="125" t="inlineStr">
+        <is>
+          <t>Veld 7C</t>
+        </is>
+      </c>
+      <c r="G337" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="338">
-      <c r="A338" s="125" t="n"/>
-      <c r="B338" s="125" t="n"/>
-      <c r="C338" s="125" t="n"/>
-      <c r="D338" s="125" t="n"/>
-      <c r="E338" s="125" t="n"/>
-      <c r="F338" s="125" t="n"/>
-      <c r="G338" s="126" t="n"/>
+      <c r="A338" s="125" t="inlineStr">
+        <is>
+          <t>Heren-4</t>
+        </is>
+      </c>
+      <c r="B338" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C338" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D338" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E338" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F338" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1A</t>
+        </is>
+      </c>
+      <c r="G338" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="339">
-      <c r="A339" s="125" t="n"/>
-      <c r="B339" s="125" t="n"/>
-      <c r="C339" s="125" t="n"/>
-      <c r="D339" s="125" t="n"/>
-      <c r="E339" s="125" t="n"/>
-      <c r="F339" s="125" t="n"/>
-      <c r="G339" s="126" t="n"/>
+      <c r="A339" s="125" t="inlineStr">
+        <is>
+          <t>Heren-5</t>
+        </is>
+      </c>
+      <c r="B339" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C339" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D339" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E339" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F339" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1B</t>
+        </is>
+      </c>
+      <c r="G339" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="340">
-      <c r="A340" s="125" t="n"/>
-      <c r="B340" s="125" t="n"/>
-      <c r="C340" s="125" t="n"/>
-      <c r="D340" s="125" t="n"/>
-      <c r="E340" s="125" t="n"/>
-      <c r="F340" s="125" t="n"/>
-      <c r="G340" s="126" t="n"/>
+      <c r="A340" s="125" t="inlineStr">
+        <is>
+          <t>Heren-6</t>
+        </is>
+      </c>
+      <c r="B340" s="125" t="inlineStr">
+        <is>
+          <t>Vrijdag</t>
+        </is>
+      </c>
+      <c r="C340" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D340" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E340" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F340" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1B</t>
+        </is>
+      </c>
+      <c r="G340" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="341">
-      <c r="A341" s="125" t="n"/>
-      <c r="B341" s="125" t="n"/>
-      <c r="C341" s="125" t="n"/>
-      <c r="D341" s="125" t="n"/>
-      <c r="E341" s="125" t="n"/>
-      <c r="F341" s="125" t="n"/>
-      <c r="G341" s="126" t="n"/>
+      <c r="A341" s="125" t="inlineStr">
+        <is>
+          <t>Heren-7</t>
+        </is>
+      </c>
+      <c r="B341" s="125" t="inlineStr">
+        <is>
+          <t>Vrijdag</t>
+        </is>
+      </c>
+      <c r="C341" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D341" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E341" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F341" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1C</t>
+        </is>
+      </c>
+      <c r="G341" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="342">
-      <c r="A342" s="125" t="n"/>
-      <c r="B342" s="125" t="n"/>
-      <c r="C342" s="125" t="n"/>
-      <c r="D342" s="125" t="n"/>
-      <c r="E342" s="125" t="n"/>
-      <c r="F342" s="125" t="n"/>
-      <c r="G342" s="126" t="n"/>
+      <c r="A342" s="125" t="inlineStr">
+        <is>
+          <t>Heren-8</t>
+        </is>
+      </c>
+      <c r="B342" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C342" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D342" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E342" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F342" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1C</t>
+        </is>
+      </c>
+      <c r="G342" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="343">
-      <c r="A343" s="125" t="n"/>
-      <c r="B343" s="125" t="n"/>
-      <c r="C343" s="125" t="n"/>
-      <c r="D343" s="125" t="n"/>
-      <c r="E343" s="125" t="n"/>
-      <c r="F343" s="125" t="n"/>
-      <c r="G343" s="126" t="n"/>
+      <c r="A343" s="125" t="inlineStr">
+        <is>
+          <t>Heren-9</t>
+        </is>
+      </c>
+      <c r="B343" s="125" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="C343" s="125" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D343" s="125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="E343" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1</t>
+        </is>
+      </c>
+      <c r="F343" s="125" t="inlineStr">
+        <is>
+          <t>Veld 1D</t>
+        </is>
+      </c>
+      <c r="G343" s="126" t="inlineStr">
+        <is>
+          <t>Ingepland</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="125" t="n"/>
@@ -21468,280 +21971,96 @@
       <c r="B470" s="101" t="n"/>
     </row>
     <row r="471">
-      <c r="A471" s="127" t="inlineStr">
-        <is>
-          <t>JO19-3</t>
-        </is>
-      </c>
-      <c r="B471" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A471" s="127" t="n"/>
+      <c r="B471" s="128" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="127" t="inlineStr">
-        <is>
-          <t>JO19-4</t>
-        </is>
-      </c>
-      <c r="B472" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A472" s="127" t="n"/>
+      <c r="B472" s="128" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="127" t="inlineStr">
-        <is>
-          <t>JO19-5</t>
-        </is>
-      </c>
-      <c r="B473" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A473" s="127" t="n"/>
+      <c r="B473" s="128" t="n"/>
     </row>
     <row r="474">
-      <c r="A474" s="127" t="inlineStr">
-        <is>
-          <t>JO19-6</t>
-        </is>
-      </c>
-      <c r="B474" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A474" s="127" t="n"/>
+      <c r="B474" s="128" t="n"/>
     </row>
     <row r="475">
-      <c r="A475" s="127" t="inlineStr">
-        <is>
-          <t>JO19-7</t>
-        </is>
-      </c>
-      <c r="B475" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A475" s="127" t="n"/>
+      <c r="B475" s="128" t="n"/>
     </row>
     <row r="476">
-      <c r="A476" s="127" t="inlineStr">
-        <is>
-          <t>JO19-8</t>
-        </is>
-      </c>
-      <c r="B476" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/2 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A476" s="127" t="n"/>
+      <c r="B476" s="128" t="n"/>
     </row>
     <row r="477">
-      <c r="A477" s="127" t="inlineStr">
-        <is>
-          <t>Heren-3</t>
-        </is>
-      </c>
-      <c r="B477" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A477" s="127" t="n"/>
+      <c r="B477" s="128" t="n"/>
     </row>
     <row r="478">
-      <c r="A478" s="127" t="inlineStr">
-        <is>
-          <t>Heren-4</t>
-        </is>
-      </c>
-      <c r="B478" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A478" s="127" t="n"/>
+      <c r="B478" s="128" t="n"/>
     </row>
     <row r="479">
-      <c r="A479" s="127" t="inlineStr">
-        <is>
-          <t>Heren-5</t>
-        </is>
-      </c>
-      <c r="B479" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A479" s="127" t="n"/>
+      <c r="B479" s="128" t="n"/>
     </row>
     <row r="480">
-      <c r="A480" s="127" t="inlineStr">
-        <is>
-          <t>Heren-6</t>
-        </is>
-      </c>
-      <c r="B480" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A480" s="127" t="n"/>
+      <c r="B480" s="128" t="n"/>
     </row>
     <row r="481">
-      <c r="A481" s="127" t="inlineStr">
-        <is>
-          <t>Heren-7</t>
-        </is>
-      </c>
-      <c r="B481" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A481" s="127" t="n"/>
+      <c r="B481" s="128" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="127" t="inlineStr">
-        <is>
-          <t>Heren-8</t>
-        </is>
-      </c>
-      <c r="B482" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A482" s="127" t="n"/>
+      <c r="B482" s="128" t="n"/>
     </row>
     <row r="483">
-      <c r="A483" s="127" t="inlineStr">
-        <is>
-          <t>Heren-9</t>
-        </is>
-      </c>
-      <c r="B483" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A483" s="127" t="n"/>
+      <c r="B483" s="128" t="n"/>
     </row>
     <row r="484">
-      <c r="A484" s="127" t="inlineStr">
-        <is>
-          <t>Heren-10</t>
-        </is>
-      </c>
-      <c r="B484" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A484" s="127" t="n"/>
+      <c r="B484" s="128" t="n"/>
     </row>
     <row r="485">
-      <c r="A485" s="127" t="inlineStr">
-        <is>
-          <t>Heren-11</t>
-        </is>
-      </c>
-      <c r="B485" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A485" s="127" t="n"/>
+      <c r="B485" s="128" t="n"/>
     </row>
     <row r="486">
-      <c r="A486" s="127" t="inlineStr">
-        <is>
-          <t>Heren-12</t>
-        </is>
-      </c>
-      <c r="B486" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A486" s="127" t="n"/>
+      <c r="B486" s="128" t="n"/>
     </row>
     <row r="487">
-      <c r="A487" s="127" t="inlineStr">
-        <is>
-          <t>Heren-13</t>
-        </is>
-      </c>
-      <c r="B487" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A487" s="127" t="n"/>
+      <c r="B487" s="128" t="n"/>
     </row>
     <row r="488">
-      <c r="A488" s="127" t="inlineStr">
-        <is>
-          <t>Heren-14</t>
-        </is>
-      </c>
-      <c r="B488" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A488" s="127" t="n"/>
+      <c r="B488" s="128" t="n"/>
     </row>
     <row r="489">
-      <c r="A489" s="127" t="inlineStr">
-        <is>
-          <t>Heren-15</t>
-        </is>
-      </c>
-      <c r="B489" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A489" s="127" t="n"/>
+      <c r="B489" s="128" t="n"/>
     </row>
     <row r="490">
-      <c r="A490" s="127" t="inlineStr">
-        <is>
-          <t>Heren-16</t>
-        </is>
-      </c>
-      <c r="B490" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A490" s="127" t="n"/>
+      <c r="B490" s="128" t="n"/>
     </row>
     <row r="491">
-      <c r="A491" s="127" t="inlineStr">
-        <is>
-          <t>Heren-18</t>
-        </is>
-      </c>
-      <c r="B491" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A491" s="127" t="n"/>
+      <c r="B491" s="128" t="n"/>
     </row>
     <row r="492">
-      <c r="A492" s="127" t="inlineStr">
-        <is>
-          <t>Heren-19</t>
-        </is>
-      </c>
-      <c r="B492" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A492" s="127" t="n"/>
+      <c r="B492" s="128" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" s="127" t="inlineStr">
-        <is>
-          <t>Dames-2</t>
-        </is>
-      </c>
-      <c r="B493" s="128" t="inlineStr">
-        <is>
-          <t>Slechts 0/1 sessies ingepland — onvoldoende veldcapaciteit</t>
-        </is>
-      </c>
+      <c r="A493" s="127" t="n"/>
+      <c r="B493" s="128" t="n"/>
     </row>
     <row r="494"/>
     <row r="495"/>
